--- a/data/trans_bre/IP16A03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 28,81</t>
+          <t>-13,18; 27,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 6,53</t>
+          <t>-27,39; 6,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 7,6</t>
+          <t>-22,17; 7,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 0,0</t>
+          <t>-16,8; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 8,0</t>
+          <t>-16,32; 7,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 0,0</t>
+          <t>-18,44; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 29,97</t>
+          <t>-11,92; 25,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,21</t>
+          <t>0,0; 24,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,97</t>
+          <t>0,0; 26,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 6,4</t>
+          <t>-19,23; 6,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,15</t>
+          <t>0,0; 13,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 0,0</t>
+          <t>-27,9; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 0,0</t>
+          <t>-33,07; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 25,88</t>
+          <t>-17,87; 25,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 27,7</t>
+          <t>-7,82; 26,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,69; -5,23</t>
+          <t>-26,5; -5,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 23,61</t>
+          <t>-4,71; 21,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 8,9</t>
+          <t>-29,05; 5,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 7,99</t>
+          <t>-13,26; 8,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,05; —</t>
+          <t>-59,57; 974,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 259,9</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 7,98</t>
+          <t>-8,46; 7,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 3,58</t>
+          <t>-18,8; 3,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,48</t>
+          <t>-6,72; 3,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,16</t>
+          <t>-3,16; 4,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -0,13</t>
+          <t>-7,35; 0,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 1,0</t>
+          <t>-4,75; 0,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-63,51; 80,24</t>
+          <t>-67,23; 72,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 200,84</t>
+          <t>-57,44; 217,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-93,5; 26,01</t>
+          <t>-93,38; 17,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-90,6; 82,78</t>
+          <t>-89,86; 79,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 27,94</t>
+          <t>-13,45; 29,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 6,29</t>
+          <t>-25,36; 6,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 7,41</t>
+          <t>-22,4; 6,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 0,0</t>
+          <t>-18,62; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 7,89</t>
+          <t>-15,81; 8,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 0,0</t>
+          <t>-18,92; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 25,54</t>
+          <t>-11,95; 24,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,89</t>
+          <t>0,0; 23,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,34</t>
+          <t>0,0; 25,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 6,45</t>
+          <t>-19,13; 6,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,14</t>
+          <t>0,0; 12,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 0,0</t>
+          <t>-23,03; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 0,0</t>
+          <t>-30,84; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 25,14</t>
+          <t>-17,53; 26,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 26,33</t>
+          <t>-7,86; 23,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,5; -5,11</t>
+          <t>-26,62; -5,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 21,42</t>
+          <t>-5,52; 23,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 5,15</t>
+          <t>-29,53; 9,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 8,94</t>
+          <t>-13,77; 7,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,57; 974,75</t>
+          <t>-60,5; 952,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 317,04</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 7,68</t>
+          <t>-8,51; 7,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 3,61</t>
+          <t>-19,34; 5,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 3,13</t>
+          <t>-6,21; 3,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 4,18</t>
+          <t>-3,28; 4,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,02</t>
+          <t>-7,17; -0,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,68</t>
+          <t>-4,67; 1,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-67,23; 72,66</t>
+          <t>-61,79; 72,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-57,44; 217,49</t>
+          <t>-56,74; 230,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-93,38; 17,24</t>
+          <t>-93,36; 29,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 79,94</t>
+          <t>-90,07; 104,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-4,91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 29,33</t>
+          <t>-14,84; 28,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 6,6</t>
+          <t>-24,69; 6,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 6,66</t>
+          <t>-24,87; 7,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 0,0</t>
+          <t>-17,63; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 8,43</t>
+          <t>-18,9; 8,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 0,0</t>
+          <t>-18,35; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 24,79</t>
+          <t>-11,88; 29,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,64</t>
+          <t>0,0; 25,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,54</t>
+          <t>0,0; 21,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 6,5</t>
+          <t>-16,78; 6,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,09</t>
+          <t>0,0; 12,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-9,0</t>
+          <t>-8,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 0,0</t>
+          <t>-30,01; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 0,0</t>
+          <t>-28,37; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 26,55</t>
+          <t>-17,91; 25,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 23,35</t>
+          <t>-7,86; 27,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-28,04%</t>
+          <t>-20,01%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,62; -5,2</t>
+          <t>-26,69; -5,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 23,24</t>
+          <t>-5,42; 23,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 9,59</t>
+          <t>-26,25; 8,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 7,11</t>
+          <t>-11,7; 8,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-60,5; 952,68</t>
+          <t>-59,05; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 317,04</t>
+          <t>-100,0; 364,81</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 7,43</t>
+          <t>-8,3; 7,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 5,06</t>
+          <t>-19,16; 3,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-51,17%</t>
+          <t>-42,14%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 3,26</t>
+          <t>-6,47; 3,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,22</t>
+          <t>-3,38; 4,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -0,04</t>
+          <t>-7,58; -0,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,37</t>
+          <t>-4,62; 1,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 72,27</t>
+          <t>-63,51; 80,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-56,74; 230,64</t>
+          <t>-59,61; 200,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-93,36; 29,08</t>
+          <t>-93,5; 26,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-90,07; 104,97</t>
+          <t>-88,42; 133,1</t>
         </is>
       </c>
     </row>
